--- a/output/graficos_dimensiones/comunal_d_env_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:30</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_maule.xlsx
@@ -51,12 +51,12 @@
     <t xml:space="preserve">Vichuquén</t>
   </si>
   <si>
+    <t xml:space="preserve">Chanco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pelarco</t>
   </si>
   <si>
-    <t xml:space="preserve">Chanco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
@@ -90,12 +90,12 @@
     <t xml:space="preserve">Linares</t>
   </si>
   <si>
+    <t xml:space="preserve">Teno</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Javier</t>
   </si>
   <si>
-    <t xml:space="preserve">Teno</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -565,7 +565,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>175.18</v>
+        <v>188.42</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>152.2</v>
+        <v>162.68</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>148.72</v>
+        <v>158.5</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>146.08</v>
+        <v>157.78</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>138.77</v>
+        <v>152.04</v>
       </c>
     </row>
     <row r="7">
@@ -644,13 +644,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7106</v>
+        <v>7202</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>128.94</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8">
@@ -661,13 +661,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7202</v>
+        <v>7106</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>127.29</v>
+        <v>137.7</v>
       </c>
     </row>
     <row r="9">
@@ -684,7 +684,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>125.99</v>
+        <v>136.39</v>
       </c>
     </row>
     <row r="10">
@@ -701,7 +701,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>122.95</v>
+        <v>131.81</v>
       </c>
     </row>
     <row r="11">
@@ -718,7 +718,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>118.82</v>
+        <v>128.38</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>112.76</v>
+        <v>121.45</v>
       </c>
     </row>
     <row r="13">
@@ -752,7 +752,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>112.5</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -769,7 +769,7 @@
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>110.9</v>
+        <v>119.96</v>
       </c>
     </row>
     <row r="15">
@@ -786,7 +786,7 @@
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>108.66</v>
+        <v>116.91</v>
       </c>
     </row>
     <row r="16">
@@ -803,7 +803,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>108.01</v>
+        <v>116.13</v>
       </c>
     </row>
     <row r="17">
@@ -820,7 +820,7 @@
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>107.02</v>
+        <v>115.68</v>
       </c>
     </row>
     <row r="18">
@@ -837,7 +837,7 @@
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>106.59</v>
+        <v>114.98</v>
       </c>
     </row>
     <row r="19">
@@ -854,7 +854,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>106.56</v>
+        <v>114.86</v>
       </c>
     </row>
     <row r="20">
@@ -865,13 +865,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>7406</v>
+        <v>7308</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>103.91</v>
+        <v>111.88</v>
       </c>
     </row>
     <row r="21">
@@ -882,13 +882,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7308</v>
+        <v>7406</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>103.57</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="22">
@@ -905,7 +905,7 @@
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>102.26</v>
+        <v>110.23</v>
       </c>
     </row>
     <row r="23">
@@ -922,7 +922,7 @@
         <v>2020</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>100.93</v>
+        <v>108.07</v>
       </c>
     </row>
     <row r="24">
@@ -939,7 +939,7 @@
         <v>2020</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>100.48</v>
+        <v>107.88</v>
       </c>
     </row>
     <row r="25">
@@ -956,7 +956,7 @@
         <v>2020</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>99.05</v>
+        <v>106.44</v>
       </c>
     </row>
     <row r="26">
@@ -973,7 +973,7 @@
         <v>2020</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>97.85</v>
+        <v>104.82</v>
       </c>
     </row>
     <row r="27">
@@ -990,7 +990,7 @@
         <v>2020</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>95.61</v>
+        <v>102.68</v>
       </c>
     </row>
     <row r="28">
@@ -1007,7 +1007,7 @@
         <v>2020</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>90.76</v>
+        <v>98.63</v>
       </c>
     </row>
     <row r="29">
@@ -1024,7 +1024,7 @@
         <v>2020</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>88.41</v>
+        <v>94.77</v>
       </c>
     </row>
     <row r="30">
@@ -1041,7 +1041,7 @@
         <v>2020</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>86.15</v>
+        <v>92.25</v>
       </c>
     </row>
     <row r="31">
@@ -1058,7 +1058,7 @@
         <v>2020</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>46.44</v>
+        <v>49.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:10</t>
+    <t xml:space="preserve">2026-10-02 16:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:10</t>
+    <t xml:space="preserve">2026-10-05 16:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
